--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UBB-FMI\UBB-FMI\An III\Sem II\VVSS\Lab\MyDrinkShop\MyDrinkShop\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munte\Desktop\VVSS\MyDrinkShopVVSS\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{916C4554-3CE5-4DA9-8A99-900E0B217D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81B23DB-8C3B-4198-AB6E-C2F734465D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="21520" windowHeight="12800" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -603,6 +601,18 @@
   </si>
   <si>
     <t>.toList()</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>Nu exista cerinte legate de fluxurile de eroare</t>
+  </si>
+  <si>
+    <t>Pag1/CF9</t>
+  </si>
+  <si>
+    <t>50 min</t>
   </si>
 </sst>
 </file>
@@ -931,6 +941,42 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -970,42 +1016,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1318,36 +1328,36 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.87890625" style="6"/>
+    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.29296875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.41015625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.87890625" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="6"/>
+    <col min="10" max="10" width="14.41015625" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.87890625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.7">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1371,10 +1381,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="43"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1389,10 +1399,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="44"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1408,19 +1418,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1436,52 +1446,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30">
-      <c r="B10" s="35">
+    <row r="10" spans="1:10" ht="28.7">
+      <c r="B10" s="22">
         <v>1</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30">
-      <c r="B11" s="38">
+    <row r="11" spans="1:10" ht="28.7">
+      <c r="B11" s="25">
+        <v>2</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.7">
+      <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C12" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30">
-      <c r="B12" s="38">
-        <v>5</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30">
+    <row r="13" spans="1:10" ht="28.7">
       <c r="B13" s="3">
-        <f t="shared" ref="B13:B23" si="0">B12+1</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>42</v>
@@ -1494,33 +1503,39 @@
       </c>
     </row>
     <row r="14" spans="1:10" customFormat="1">
-      <c r="B14" s="41">
+      <c r="B14" s="28">
         <f>B13+1</f>
-        <v>7</v>
-      </c>
-      <c r="C14" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="29" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="3">
         <f>B14+1</f>
-        <v>8</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" ref="B13:B23" si="0">B15+1</f>
+        <v>7</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1529,7 +1544,7 @@
     <row r="17" spans="2:5">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1538,7 +1553,7 @@
     <row r="18" spans="2:5">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1547,7 +1562,7 @@
     <row r="19" spans="2:5">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1556,7 +1571,7 @@
     <row r="20" spans="2:5">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1565,7 +1580,7 @@
     <row r="21" spans="2:5">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1574,7 +1589,7 @@
     <row r="22" spans="2:5">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1583,7 +1598,7 @@
     <row r="23" spans="2:5">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1595,7 +1610,7 @@
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="1" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1618,35 +1633,35 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.87890625" style="6"/>
+    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.29296875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.41015625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.87890625" style="6"/>
+    <col min="9" max="9" width="22.1171875" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.87890625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.7">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1670,17 +1685,17 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="27"/>
+      <c r="E4" s="45"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="41">
+      <c r="J4" s="28">
         <v>234</v>
       </c>
     </row>
@@ -1688,17 +1703,17 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="47"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="28">
         <v>234</v>
       </c>
     </row>
@@ -1707,19 +1722,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1735,7 +1750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="165">
+    <row r="10" spans="1:10" ht="143.35">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1745,26 +1760,26 @@
       <c r="D10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="33" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="105">
+    <row r="11" spans="1:10" ht="86">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="31" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="37" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="75">
+    <row r="12" spans="1:10" ht="57.35">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
@@ -1772,14 +1787,14 @@
       <c r="C12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="33" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="120">
+    <row r="13" spans="1:10" ht="100.35">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1787,10 +1802,10 @@
       <c r="C13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="33" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1800,8 +1815,8 @@
         <v>5</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="52"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="39"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="3">
@@ -1809,8 +1824,8 @@
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="52"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="39"/>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="3">
@@ -1818,8 +1833,8 @@
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="52"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="39"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="3">
@@ -1827,8 +1842,8 @@
         <v>8</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="52"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="39"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="3">
@@ -1837,7 +1852,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="51"/>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="3">
@@ -1940,36 +1955,36 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.87890625" style="6"/>
+    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="54.29296875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="5" max="5" width="41.41015625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.87890625" style="6"/>
+    <col min="9" max="9" width="26.703125" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.87890625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.7">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1982,7 +1997,7 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="28" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="17">
@@ -1993,14 +2008,14 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="48"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="28" t="s">
         <v>47</v>
       </c>
       <c r="J4" s="3">
@@ -2011,14 +2026,14 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="32"/>
+      <c r="E5" s="50"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="28" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="3">
@@ -2030,19 +2045,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -2058,7 +2073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30">
+    <row r="10" spans="1:10" ht="28.7">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -2068,11 +2083,11 @@
       <c r="D10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="32" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30">
+    <row r="11" spans="1:10" ht="28.7">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -2087,7 +2102,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="45">
+    <row r="12" spans="1:10" ht="43">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -2102,7 +2117,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="90">
+    <row r="13" spans="1:10" ht="71.7">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2117,7 +2132,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="75">
+    <row r="14" spans="1:10" ht="71.7">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2305,37 +2320,37 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.87890625" style="6"/>
+    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.29296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.1171875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.87890625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5859375" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.87890625" style="6"/>
+    <col min="9" max="9" width="26.703125" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.87890625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.7">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -2348,7 +2363,7 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="28" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="17">
@@ -2359,14 +2374,14 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="48"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="J4" s="3">
@@ -2377,14 +2392,14 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="22"/>
+      <c r="E5" s="40"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="28" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="3">
@@ -2396,10 +2411,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="40"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10">
@@ -2419,7 +2434,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="105">
+    <row r="10" spans="1:10" ht="86">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -2447,12 +2462,12 @@
       <c r="D11" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="34" t="s">
         <v>82</v>
       </c>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="135">
+    <row r="12" spans="1:10" ht="100.35">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -2470,7 +2485,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="45">
+    <row r="13" spans="1:10" ht="28.7">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2488,7 +2503,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30">
+    <row r="14" spans="1:10" ht="28.7">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2506,7 +2521,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="30">
+    <row r="15" spans="1:10" ht="28.7">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2675,11 +2690,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
       <c r="F32" s="18" t="s">
         <v>59</v>
       </c>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munte\Desktop\VVSS\MyDrinkShopVVSS\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UBB-FMI\UBB-FMI\An III\Sem II\VVSS\Lab\MyDrinkShop\MyDrinkShop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81B23DB-8C3B-4198-AB6E-C2F734465D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F007C9CA-5EF1-4808-834A-2E7FB353C69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="21520" windowHeight="12800" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="112">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -168,9 +168,6 @@
     <t>C01 (Decision logic is erroneous or inadequate)</t>
   </si>
   <si>
-    <t>C12 (Variable type and dimensions are incorrectly declared)</t>
-  </si>
-  <si>
     <t>C06 (Errors in preparing or processing input data)</t>
   </si>
   <si>
@@ -183,9 +180,6 @@
     <t>30 min</t>
   </si>
   <si>
-    <t xml:space="preserve">C07 (Output processing errors exist) </t>
-  </si>
-  <si>
     <t>Mutu Vlad, Munteanu Mihai, Moghioros Eric</t>
   </si>
   <si>
@@ -199,15 +193,6 @@
   </si>
   <si>
     <t>Pag1/CF6</t>
-  </si>
-  <si>
-    <t>metoda service.comandaProdus()  nu este apelata niciodata.</t>
-  </si>
-  <si>
-    <t>metoda generateReceipt nu salveaza un fisier .csv specific bonului</t>
-  </si>
-  <si>
-    <t>In entitatea Stoc, atributele cantitate și stocMinim sunt declarate ca double, dar constructorul accepta parametri int</t>
   </si>
   <si>
     <r>
@@ -354,9 +339,6 @@
     <t>pag1/cf7</t>
   </si>
   <si>
-    <t>pag1/cf4 si cf5</t>
-  </si>
-  <si>
     <t>Nu este specificat cum poti actualiza un produs(care sunt fieldurile lui)</t>
   </si>
   <si>
@@ -613,6 +595,42 @@
   </si>
   <si>
     <t>50 min</t>
+  </si>
+  <si>
+    <t>metoda service.comandaProdus()  nu este apelata niciodata. Nu se consuma stocul</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>ramificatiile sunt construite corect</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>nu este cazul N/A</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>Nu exista try-catch in filerepo pentru numere double, si pot aparea erori de tipul NumberFormatException</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05 (Subprogram invocations are violated.) </t>
+  </si>
+  <si>
+    <t>pag1/cnf6</t>
+  </si>
+  <si>
+    <t>Nu exista try-catch in controller pentru prinderea erorilor de validare</t>
+  </si>
+  <si>
+    <t>C11 (Errors are made in writing out variable names.)</t>
+  </si>
+  <si>
+    <t>Denumirile variabilelor nu sunt consecvente</t>
   </si>
 </sst>
 </file>
@@ -957,9 +975,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1016,6 +1031,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1031,10 +1049,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1328,36 +1342,36 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.87890625" style="6"/>
-    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.29296875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.41015625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.87890625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.41015625" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.87890625" style="6"/>
+    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.7">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1381,10 +1395,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="43"/>
+      <c r="E4" s="42"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1399,10 +1413,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="44"/>
+      <c r="E5" s="43"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1418,19 +1432,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="40"/>
+      <c r="E7" s="39"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1446,7 +1460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.7">
+    <row r="10" spans="1:10" ht="30">
       <c r="B10" s="22">
         <v>1</v>
       </c>
@@ -1454,13 +1468,13 @@
         <v>38</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" s="24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.7">
+    <row r="11" spans="1:10" ht="30">
       <c r="B11" s="25">
         <v>2</v>
       </c>
@@ -1468,13 +1482,13 @@
         <v>40</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.7">
+    <row r="12" spans="1:10" ht="30">
       <c r="B12" s="25">
         <v>3</v>
       </c>
@@ -1482,13 +1496,13 @@
         <v>40</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.7">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30">
       <c r="B13" s="3">
         <v>4</v>
       </c>
@@ -1496,10 +1510,10 @@
         <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:10" customFormat="1">
@@ -1508,13 +1522,13 @@
         <v>5</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1523,18 +1537,18 @@
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="3">
-        <f t="shared" ref="B13:B23" si="0">B15+1</f>
+        <f t="shared" ref="B16:B23" si="0">B15+1</f>
         <v>7</v>
       </c>
       <c r="C16" s="3"/>
@@ -1610,7 +1624,7 @@
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1633,35 +1647,35 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.87890625" style="6"/>
-    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.29296875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.41015625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.87890625" style="6"/>
-    <col min="9" max="9" width="22.1171875" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.87890625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.7">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1685,10 +1699,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="45"/>
+      <c r="E4" s="44"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1703,10 +1717,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="47"/>
+      <c r="E5" s="46"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1722,19 +1736,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="40"/>
+      <c r="E7" s="39"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1750,63 +1764,63 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="143.35">
+    <row r="10" spans="1:10" ht="165">
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="86">
+        <v>72</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="105">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="57.35">
+        <v>75</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="75">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="100.35">
+        <v>77</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="120">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="32" t="s">
         <v>93</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1815,8 +1829,8 @@
         <v>5</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="39"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="38"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="3">
@@ -1824,8 +1838,8 @@
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="39"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="3">
@@ -1833,8 +1847,8 @@
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="39"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="38"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="3">
@@ -1842,8 +1856,8 @@
         <v>8</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="39"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="38"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="3">
@@ -1852,7 +1866,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="38"/>
+      <c r="E18" s="37"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="3">
@@ -1955,36 +1969,36 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.87890625" style="6"/>
-    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="54.29296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.41015625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.87890625" style="6"/>
-    <col min="9" max="9" width="26.703125" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.87890625" style="6"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.7">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -2008,15 +2022,15 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="48"/>
+      <c r="E4" s="47"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3">
         <v>234</v>
@@ -2026,10 +2040,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="50"/>
+      <c r="E5" s="49"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -2045,19 +2059,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="40"/>
+      <c r="E7" s="39"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -2073,7 +2087,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.7">
+    <row r="10" spans="1:10" ht="30">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -2081,70 +2095,68 @@
         <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.7">
+        <v>61</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="43">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="90">
+      <c r="B13" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="71.7">
-      <c r="B13" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="75">
+      <c r="B14" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="71.7">
-      <c r="B14" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2152,27 +2164,39 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5">
+      <c r="E16" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="45">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="3">
@@ -2297,7 +2321,7 @@
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2320,37 +2344,37 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.87890625" style="6"/>
-    <col min="2" max="2" width="12.29296875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="18.29296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.1171875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.87890625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.5859375" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.87890625" style="6"/>
-    <col min="9" max="9" width="26.703125" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.87890625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.7">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -2374,10 +2398,10 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="48"/>
+      <c r="E4" s="47"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -2392,10 +2416,10 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="40"/>
+      <c r="D5" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="39"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -2411,10 +2435,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10">
@@ -2434,21 +2458,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="86">
+    <row r="10" spans="1:10" ht="105">
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2457,86 +2481,86 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>82</v>
+        <v>74</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>76</v>
       </c>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="100.35">
+    <row r="12" spans="1:10" ht="135">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="45">
+      <c r="B13" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.7">
-      <c r="B13" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:10" ht="30">
+      <c r="B14" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30">
+      <c r="B15" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="28.7">
-      <c r="B14" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.7">
-      <c r="B15" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2690,13 +2714,13 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
       <c r="F32" s="18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="6:6">
